--- a/Reporte_gastos/tabla_gastos_zonas_2026-5.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-5.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">TIENDA</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incentivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_sueldos</t>
   </si>
   <si>
     <t xml:space="preserve">Alquileres</t>
@@ -425,326 +434,461 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>46311462.18</v>
       </c>
       <c r="C2" t="n">
+        <v>4424016.01738636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>106764</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1331587.43062313</v>
+      </c>
+      <c r="F2" t="n">
         <v>5862367.44800949</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>7050000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>381156.89</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>7431156.89</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>2201042.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>14240375.09</v>
       </c>
       <c r="C3" t="n">
+        <v>2633715.57630364</v>
+      </c>
+      <c r="D3" t="n">
+        <v>83679</v>
+      </c>
+      <c r="E3" t="n">
+        <v>800650.12318446</v>
+      </c>
+      <c r="F3" t="n">
         <v>3518044.6994881</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>2504086.52</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2420500.26</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4924586.78</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>420001.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>60551837.27</v>
       </c>
       <c r="C4" t="n">
+        <v>7057731.59369</v>
+      </c>
+      <c r="D4" t="n">
+        <v>190443</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2132237.55380759</v>
+      </c>
+      <c r="F4" t="n">
         <v>9380412.14749759</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>9554086.52</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>2801657.15</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>12355743.67</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>2621044.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>33349969.95</v>
       </c>
       <c r="C5" t="n">
+        <v>2726433.32566038</v>
+      </c>
+      <c r="D5" t="n">
+        <v>160563</v>
+      </c>
+      <c r="E5" t="n">
+        <v>851138.237018774</v>
+      </c>
+      <c r="F5" t="n">
         <v>3738134.56267915</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>2056151.52</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>672700.36</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>2728851.88</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>358009.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>19982040.59</v>
       </c>
       <c r="C6" t="n">
+        <v>2523581.60058962</v>
+      </c>
+      <c r="D6" t="n">
+        <v>66077</v>
+      </c>
+      <c r="E6" t="n">
+        <v>762936.161995914</v>
+      </c>
+      <c r="F6" t="n">
         <v>3352594.76258554</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>923100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>290225.35</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1213325.35</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>536641.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>53332010.54</v>
       </c>
       <c r="C7" t="n">
+        <v>5250014.92625</v>
+      </c>
+      <c r="D7" t="n">
+        <v>226640</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1614074.39901469</v>
+      </c>
+      <c r="F7" t="n">
         <v>7090729.32526469</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>2979251.52</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>962925.71</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>3942177.23</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>894651.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>1967146.4</v>
       </c>
       <c r="C8" t="n">
+        <v>1005749.6525</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17857</v>
+      </c>
+      <c r="E8" t="n">
+        <v>302105.094396346</v>
+      </c>
+      <c r="F8" t="n">
         <v>1325711.74689635</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>715965.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>383750.2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>1099715.74</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>320450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>4196030.03</v>
       </c>
       <c r="C9" t="n">
+        <v>2341943.81375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40535</v>
+      </c>
+      <c r="E9" t="n">
+        <v>699835.442320313</v>
+      </c>
+      <c r="F9" t="n">
         <v>3082314.25607031</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>1079060</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>672700.36</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>1751760.36</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>263897.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>6163176.43</v>
       </c>
       <c r="C10" t="n">
+        <v>3347693.46625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>58392</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1001940.53671666</v>
+      </c>
+      <c r="F10" t="n">
         <v>4408026.00296666</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>1795025.54</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>1056450.56</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>2851476.1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>584347.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>7131739.87</v>
       </c>
       <c r="C11" t="n">
+        <v>1680527.76351743</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>492646.623198825</v>
+      </c>
+      <c r="F11" t="n">
         <v>2173174.38671626</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>565405.38</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>58711.23</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>624116.61</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>51746.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>8053769.91</v>
       </c>
       <c r="C12" t="n">
+        <v>3645168.90648257</v>
+      </c>
+      <c r="D12" t="n">
+        <v>42786</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1079633.14332733</v>
+      </c>
+      <c r="F12" t="n">
         <v>4767588.0498099</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>1822860.48</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>184127.32</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>2006987.8</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>46314.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>15185509.78</v>
       </c>
       <c r="C13" t="n">
+        <v>5325696.67</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42786</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1572279.76652615</v>
+      </c>
+      <c r="F13" t="n">
         <v>6940762.43652615</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>2388265.86</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>242838.55</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>2631104.41</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>98060.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>16696715.19</v>
       </c>
       <c r="C14" t="n">
+        <v>2565008.21</v>
+      </c>
+      <c r="D14" t="n">
+        <v>77572</v>
+      </c>
+      <c r="E14" t="n">
+        <v>774275.084025</v>
+      </c>
+      <c r="F14" t="n">
         <v>3416855.294025</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>1047092</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>1345400.72</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>2392492.72</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>383313.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>151929249.21</v>
       </c>
       <c r="C15" t="n">
+        <v>23546144.86619</v>
+      </c>
+      <c r="D15" t="n">
+        <v>595833</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7094807.34009008</v>
+      </c>
+      <c r="F15" t="n">
         <v>31236785.2062801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>17763721.44</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>6409272.69</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>24172994.13</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>4581417.19</v>
       </c>
     </row>
